--- a/quizzes/024_protein_structure_vocabulary_quiz--quizzes.xlsx
+++ b/quizzes/024_protein_structure_vocabulary_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>general_awareness</t>
+          <t>protein_structure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>General Awareness</t>
+          <t>Protein Structure</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Primary vs Secondary Structure</t>
+          <t>Primary/Secondary Structure</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>protein_function</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tertiary Structure</t>
+          <t>Protein Function</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>protein_function</t>
+          <t>subunits</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Protein Function</t>
+          <t>Subunits</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>subunits</t>
+          <t>protein_folding</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Subunits</t>
+          <t>Protein Folding</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>protein_folding</t>
+          <t>disulfide_bond</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Protein Folding</t>
+          <t>Disulfide Bond</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>disulfide_bond</t>
+          <t>protein_ligand</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Disulfide Bond</t>
+          <t>Protein Ligand</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>protein_ligand</t>
+          <t>protein_synthesis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Protein Ligand</t>
+          <t>Protein Synthesis</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>protein_synthesis</t>
+          <t>protein_classification</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Protein Synthesis</t>
+          <t>Protein Classification</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>protein_classification</t>
+          <t>quaternary_structure</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Protein Classification</t>
+          <t>Quaternary Structure</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>protein_structure</t>
+          <t>protein_synthesis_method</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Protein Structure</t>
+          <t>Protein Synthesis Method</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>disulfide_bond_role</t>
+          <t>protein_functional_group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Disulfide Bond Role</t>
+          <t>Functional Group</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>quaternary_structure</t>
+          <t>protein_folding_method</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Quaternary Structure</t>
+          <t>Folding Method</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>protein_synthesis_method</t>
+          <t>protein_3d_structure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Protein Synthesis Method</t>
+          <t>3D Structure</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>protein_functional_group</t>
+          <t>protein_classification_category</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Functional Group</t>
+          <t>Classification Category</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>protein_classification_method</t>
+          <t>protein_folding_type</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Classification Method</t>
+          <t>Folding Type</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>protein_functional_group</t>
+          <t>disulfide_bond_type</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Functional Group</t>
+          <t>Disulfide Bond Type</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>protein_thermodynamics</t>
+          <t>protein_structure_type</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thermodynamics</t>
+          <t>Protein Structure Type</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>protein_folding_method</t>
+          <t>protein_thermodynamics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Folding Method</t>
+          <t>Thermodynamics</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>disulfide_bond_type</t>
+          <t>protein_ligand_function</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Disulfide Bond Type</t>
+          <t>Ligand Function</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>protein_ligand_function</t>
+          <t>protein_classification_process</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ligand Function</t>
+          <t>Classification Process</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>protein_classification_category</t>
+          <t>protein_folding_process</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Classification Category</t>
+          <t>Folding Process</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>protein_folding_type</t>
+          <t>protein_3d_structure_type</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Folding Type</t>
+          <t>3D Structure Type</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>disulfide_bond_type</t>
+          <t>protein_synthesis_process</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Disulfide Bond Type</t>
+          <t>Synthesis Process</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>protein_structure_type</t>
+          <t>disulfide_bond_role</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Protein Structure Type</t>
+          <t>Disulfide Bond Role</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>protein_synthesis_process</t>
+          <t>protein_classification_category_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Synthesis Process</t>
+          <t>Protein Classification Category 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1113,17 +1113,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>protein_3d_structure</t>
+          <t>protein_folding_type_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3D Structure</t>
+          <t>Protein Folding Type 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>protein_functional_group</t>
+          <t>disulfide_bond_type_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Functional Group</t>
+          <t>Disulfide Bond Type 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>disulfide_bond_role</t>
+          <t>protein_structure_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Disulfide Bond Role</t>
+          <t>Protein Structure 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>protein_classification</t>
+          <t>protein_classification_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Protein Classification</t>
+          <t>Protein Classification 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>disulfide_bond_type</t>
+          <t>disulfide_bond_role_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Disulfide Bond Type</t>
+          <t>Disulfide Bond Role 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>protein_structure</t>
+          <t>protein_folding_method_2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Protein Structure</t>
+          <t>Protein Folding Method 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1251,17 +1251,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>protein_classification_category</t>
+          <t>protein_3d_structure_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Classification Category</t>
+          <t>Protein 3D Structure 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>protein_folding_method</t>
+          <t>protein_classification_category_3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Folding Method</t>
+          <t>Protein Classification Category 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>protein_3d_structure_type</t>
+          <t>protein_folding_type_3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3D Structure</t>
+          <t>Protein Folding Type 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>disulfide_bond_role</t>
+          <t>disulfide_bond_type_3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Disulfide Bond Role</t>
+          <t>Disulfide Bond Type 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>protein_folding_type</t>
+          <t>protein_structure_type_2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Folding Type</t>
+          <t>Protein Structure Type 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1366,136 +1366,21 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>protein_classification_type</t>
+          <t>protein_thermodynamics_2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Classification Type</t>
+          <t>Protein Thermodynamics 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>protein_synthesis_process</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Synthesis Process</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>protein_3d_structure</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>3D Structure</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>disulfide_bond_type</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Disulfide Bond Type</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>protein_synthesis_method</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Synthesis Method</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>protein_structure_type</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Protein Structure Type</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1512,10 +1397,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C140"/>
+  <dimension ref="A1:C122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1540,7 +1425,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>general_awareness_choices</t>
+          <t>protein_structure_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1557,7 +1442,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>general_awareness_choices</t>
+          <t>protein_structure_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1574,7 +1459,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>general_awareness_choices</t>
+          <t>protein_structure_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1664,29 +1549,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sheet</t>
+          <t>Rods</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>primary_secondary_choices</t>
+          <t>protein_function_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>enzymes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rods</t>
+          <t>Enzymes</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1583,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>enzymes</t>
+          <t>structural_proteins</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Enzymes</t>
+          <t>Structural proteins</t>
         </is>
       </c>
     </row>
@@ -1715,29 +1600,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>structural_proteins</t>
+          <t>transporter_proteins</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Structural proteins</t>
+          <t>Transporter proteins</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>protein_function_choices</t>
+          <t>protein_folding_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>transporter_proteins</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Transporter proteins</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1749,29 +1634,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>protein_folding_choices</t>
+          <t>disulfide_bond_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1668,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1800,29 +1685,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>disulfide_bond_choices</t>
+          <t>protein_ligand_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_sure</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Not Sure</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1834,29 +1719,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>protein_ligand_choices</t>
+          <t>protein_synthesis_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>transcription</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Transcription</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1753,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>transcription</t>
+          <t>translation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Transcription</t>
+          <t>Translation</t>
         </is>
       </c>
     </row>
@@ -1885,29 +1770,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>translation</t>
+          <t>folding</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Translation</t>
+          <t>Folding</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>protein_synthesis_choices</t>
+          <t>protein_classification_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>folding</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Folding</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1919,573 +1804,573 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>protein_classification_choices</t>
+          <t>quaternary_structure_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>alpha_helix</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Alpha Helix</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>protein_structure_choices</t>
+          <t>quaternary_structure_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>alpha_helix</t>
+          <t>beta_sheet</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpha Helix</t>
+          <t>Beta Sheet</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>protein_structure_choices</t>
+          <t>quaternary_structure_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>beta_sheet</t>
+          <t>coil</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Beta Sheet</t>
+          <t>Coil</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>protein_structure_choices</t>
+          <t>protein_synthesis_method_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>coil</t>
+          <t>in_vivo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Coil</t>
+          <t>In Vivo</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>protein_synthesis_method_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>enzymatic_activity</t>
+          <t>in_vitro</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Enzymatic activity</t>
+          <t>In Vitro</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>protein_synthesis_method_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>folding</t>
+          <t>prokaryotic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Folding</t>
+          <t>Prokaryotic</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>protein_functional_group_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ligand</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ligand</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>protein_functional_group_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>protein_folding_method_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>transport</t>
+          <t>in_vivo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>In Vivo</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>quaternary_structure_choices</t>
+          <t>protein_folding_method_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>alpha_helix</t>
+          <t>in_vitro</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alpha Helix</t>
+          <t>In Vitro</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>quaternary_structure_choices</t>
+          <t>protein_folding_method_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>beta_sheet</t>
+          <t>in_silico</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Beta Sheet</t>
+          <t>In Silico</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>quaternary_structure_choices</t>
+          <t>protein_3d_structure_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>coil</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Coil</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>protein_synthesis_method_choices</t>
+          <t>protein_3d_structure_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>in_vitro</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>In Vitro</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>protein_synthesis_method_choices</t>
+          <t>protein_classification_category_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>in_vivo</t>
+          <t>enzyme</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>In Vivo</t>
+          <t>Enzyme</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>protein_synthesis_method_choices</t>
+          <t>protein_classification_category_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>prokaryotic</t>
+          <t>hormone</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Prokaryotic</t>
+          <t>Hormone</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>protein_functional_group_choices</t>
+          <t>protein_classification_category_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>enzyme</t>
+          <t>receptor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Enzyme</t>
+          <t>Receptor</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>protein_functional_group_choices</t>
+          <t>protein_classification_category_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>hormone</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hormone</t>
+          <t>Transport</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>protein_functional_group_choices</t>
+          <t>protein_folding_type_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ligand</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ligand</t>
+          <t>Alpha</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>protein_functional_group_choices</t>
+          <t>protein_folding_type_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>receptor</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Receptor</t>
+          <t>Beta</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>protein_classification_method_choices</t>
+          <t>protein_folding_type_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>homology</t>
+          <t>coil</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Homology</t>
+          <t>Coil</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>protein_classification_method_choices</t>
+          <t>disulfide_bond_type_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>paralog</t>
+          <t>cystein</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Paralog</t>
+          <t>Cystein</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>protein_classification_method_choices</t>
+          <t>disulfide_bond_type_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>prokaryote</t>
+          <t>hydrogen_bond</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Prokaryote</t>
+          <t>Hydrogen bond</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>protein_functional_group_choices</t>
+          <t>disulfide_bond_type_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>imino_bond</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Imino bond</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>protein_functional_group_choices</t>
+          <t>disulfide_bond_type_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>van_der_waals</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Van der Waals</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>protein_thermodynamics_choices</t>
+          <t>protein_structure_type_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>alpha_helix</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Alpha Helix</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>protein_thermodynamics_choices</t>
+          <t>protein_structure_type_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>beta_sheet</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Beta Sheet</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>protein_folding_method_choices</t>
+          <t>protein_structure_type_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>in_vivo</t>
+          <t>coil</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>In Vivo</t>
+          <t>Coil</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>protein_folding_method_choices</t>
+          <t>protein_structure_type_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>in_vitro</t>
+          <t>globular</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>In Vitro</t>
+          <t>Globular</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>protein_folding_method_choices</t>
+          <t>protein_structure_type_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>in_silico</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>In Silico</t>
+          <t>Rods</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>disulfide_bond_type_choices</t>
+          <t>protein_thermodynamics_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>cystein</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cystein</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>disulfide_bond_type_choices</t>
+          <t>protein_thermodynamics_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>hydrogen_bond</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hydrogen bond</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>disulfide_bond_type_choices</t>
+          <t>protein_ligand_function_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>imino_bond</t>
+          <t>allosteric</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Imino bond</t>
+          <t>Allosteric</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>disulfide_bond_type_choices</t>
+          <t>protein_ligand_function_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>van_der_waals</t>
+          <t>allosteric_effect</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Van der Waals</t>
+          <t>Allosteric effect</t>
         </is>
       </c>
     </row>
@@ -2497,12 +2382,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>allosteric</t>
+          <t>enzyme_activation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Allosteric</t>
+          <t>Enzyme activation</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2399,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>allosteric_effect</t>
+          <t>ligand_binding</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Allosteric effect</t>
+          <t>Ligand binding</t>
         </is>
       </c>
     </row>
@@ -2531,563 +2416,563 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>enzyme_activation</t>
+          <t>transducer</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Enzyme activation</t>
+          <t>Transducer</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>protein_ligand_function_choices</t>
+          <t>protein_classification_process_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ligand_binding</t>
+          <t>enzyme</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ligand binding</t>
+          <t>Enzyme</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>protein_ligand_function_choices</t>
+          <t>protein_classification_process_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>transducer</t>
+          <t>hormone</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Transducer</t>
+          <t>Hormone</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>protein_classification_category_choices</t>
+          <t>protein_classification_process_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>enzyme</t>
+          <t>receptor</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Enzyme</t>
+          <t>Receptor</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>protein_classification_category_choices</t>
+          <t>protein_classification_process_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>hormone</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hormone</t>
+          <t>Transport</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>protein_classification_category_choices</t>
+          <t>protein_folding_process_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>receptor</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Receptor</t>
+          <t>Alpha</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>protein_classification_category_choices</t>
+          <t>protein_folding_process_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>transport</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Beta</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>protein_folding_type_choices</t>
+          <t>protein_folding_process_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>coil</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Coil</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>protein_folding_type_choices</t>
+          <t>protein_3d_structure_type_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>alpha_helix</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Alpha Helix</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>protein_folding_type_choices</t>
+          <t>protein_3d_structure_type_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>coil</t>
+          <t>beta_sheet</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Coil</t>
+          <t>Beta Sheet</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>disulfide_bond_type_choices</t>
+          <t>protein_3d_structure_type_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>cystein</t>
+          <t>coil</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cystein</t>
+          <t>Coil</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>disulfide_bond_type_choices</t>
+          <t>protein_synthesis_process_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>hydrogen_bond</t>
+          <t>in_vivo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hydrogen bond</t>
+          <t>In Vivo</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>disulfide_bond_type_choices</t>
+          <t>protein_synthesis_process_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>imino_bond</t>
+          <t>in_vitro</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Imino bond</t>
+          <t>In Vitro</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>disulfide_bond_type_choices</t>
+          <t>protein_synthesis_process_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>van_der_waals</t>
+          <t>in_silico</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Van der Waals</t>
+          <t>In Silico</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>protein_structure_type_choices</t>
+          <t>disulfide_bond_role_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>alpha_helix</t>
+          <t>enzymatic_activity</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Alpha Helix</t>
+          <t>Enzymatic activity</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>protein_structure_type_choices</t>
+          <t>disulfide_bond_role_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>beta_sheet</t>
+          <t>folding</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Beta Sheet</t>
+          <t>Folding</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>protein_structure_type_choices</t>
+          <t>disulfide_bond_role_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>coil</t>
+          <t>ligand</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Coil</t>
+          <t>Ligand</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>protein_structure_type_choices</t>
+          <t>disulfide_bond_role_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>globular</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Globular</t>
+          <t>Structural</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>protein_structure_type_choices</t>
+          <t>disulfide_bond_role_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>rods</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Rods</t>
+          <t>Transport</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>protein_synthesis_process_choices</t>
+          <t>protein_classification_category_2_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>in_vivo</t>
+          <t>enzyme</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>In Vivo</t>
+          <t>Enzyme</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>protein_synthesis_process_choices</t>
+          <t>protein_classification_category_2_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>in_vitro</t>
+          <t>hormone</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>In Vitro</t>
+          <t>Hormone</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>protein_synthesis_process_choices</t>
+          <t>protein_classification_category_2_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>in_silico</t>
+          <t>receptor</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>In Silico</t>
+          <t>Receptor</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>protein_3d_structure_choices</t>
+          <t>protein_classification_category_2_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Transport</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>protein_3d_structure_choices</t>
+          <t>protein_folding_type_2_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Alpha</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>protein_functional_group_choices</t>
+          <t>protein_folding_type_2_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>enzyme</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Enzyme</t>
+          <t>Beta</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>protein_functional_group_choices</t>
+          <t>protein_folding_type_2_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>hormone</t>
+          <t>coil</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hormone</t>
+          <t>Coil</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>protein_functional_group_choices</t>
+          <t>disulfide_bond_type_2_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ligand</t>
+          <t>cystein</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ligand</t>
+          <t>Cystein</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>protein_functional_group_choices</t>
+          <t>disulfide_bond_type_2_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>receptor</t>
+          <t>hydrogen_bond</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Receptor</t>
+          <t>Hydrogen bond</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>disulfide_bond_type_2_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>enzymatic_activity</t>
+          <t>imino_bond</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Enzymatic activity</t>
+          <t>Imino bond</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>disulfide_bond_type_2_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>folding</t>
+          <t>van_der_waals</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Folding</t>
+          <t>Van der Waals</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>protein_structure_2_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ligand</t>
+          <t>alpha_helix</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ligand</t>
+          <t>Alpha Helix</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>protein_structure_2_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>beta_sheet</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Beta Sheet</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>protein_structure_2_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>transport</t>
+          <t>coil</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Coil</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>protein_classification_choices</t>
+          <t>protein_classification_2_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3104,7 +2989,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>protein_classification_choices</t>
+          <t>protein_classification_2_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3121,279 +3006,279 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>disulfide_bond_type_choices</t>
+          <t>disulfide_bond_role_2_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>cystein</t>
+          <t>enzymatic_activity</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cystein</t>
+          <t>Enzymatic activity</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>disulfide_bond_type_choices</t>
+          <t>disulfide_bond_role_2_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>hydrogen_bond</t>
+          <t>folding</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hydrogen bond</t>
+          <t>Folding</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>disulfide_bond_type_choices</t>
+          <t>disulfide_bond_role_2_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>imino_bond</t>
+          <t>ligand</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Imino bond</t>
+          <t>Ligand</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>disulfide_bond_type_choices</t>
+          <t>disulfide_bond_role_2_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>van_der_waals</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Van der Waals</t>
+          <t>Structural</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>protein_structure_choices</t>
+          <t>disulfide_bond_role_2_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>alpha_helix</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Alpha Helix</t>
+          <t>Transport</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>protein_structure_choices</t>
+          <t>protein_folding_method_2_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>beta_sheet</t>
+          <t>in_vivo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Beta Sheet</t>
+          <t>In Vivo</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>protein_structure_choices</t>
+          <t>protein_folding_method_2_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>coil</t>
+          <t>in_vitro</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Coil</t>
+          <t>In Vitro</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>protein_classification_category_choices</t>
+          <t>protein_folding_method_2_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>enzyme</t>
+          <t>in_silico</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Enzyme</t>
+          <t>In Silico</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>protein_classification_category_choices</t>
+          <t>protein_3d_structure_2_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>hormone</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hormone</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>protein_classification_category_choices</t>
+          <t>protein_3d_structure_2_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>receptor</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Receptor</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>protein_classification_category_choices</t>
+          <t>protein_classification_category_3_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>transport</t>
+          <t>enzyme</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Enzyme</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>protein_folding_method_choices</t>
+          <t>protein_classification_category_3_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>in_vivo</t>
+          <t>hormone</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>In Vivo</t>
+          <t>Hormone</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>protein_folding_method_choices</t>
+          <t>protein_classification_category_3_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>in_vitro</t>
+          <t>receptor</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>In Vitro</t>
+          <t>Receptor</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>protein_folding_method_choices</t>
+          <t>protein_classification_category_3_choices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>in_silico</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>In Silico</t>
+          <t>Transport</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>protein_3d_structure_type_choices</t>
+          <t>protein_folding_type_3_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>alpha_helix</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Alpha Helix</t>
+          <t>Alpha</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>protein_3d_structure_type_choices</t>
+          <t>protein_folding_type_3_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>beta_sheet</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Beta Sheet</t>
+          <t>Beta</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>protein_3d_structure_type_choices</t>
+          <t>protein_folding_type_3_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3410,493 +3295,187 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>disulfide_bond_type_3_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>enzymatic_activity</t>
+          <t>cystein</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Enzymatic activity</t>
+          <t>Cystein</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>disulfide_bond_type_3_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>folding</t>
+          <t>hydrogen_bond</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Folding</t>
+          <t>Hydrogen bond</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>disulfide_bond_type_3_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ligand</t>
+          <t>imino_bond</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ligand</t>
+          <t>Imino bond</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>disulfide_bond_type_3_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>van_der_waals</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Van der Waals</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>disulfide_bond_role_choices</t>
+          <t>protein_structure_type_2_choices</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>transport</t>
+          <t>alpha_helix</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Alpha Helix</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>protein_folding_type_choices</t>
+          <t>protein_structure_type_2_choices</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>beta_sheet</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Beta Sheet</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>protein_folding_type_choices</t>
+          <t>protein_structure_type_2_choices</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>coil</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Coil</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>protein_folding_type_choices</t>
+          <t>protein_structure_type_2_choices</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>coil</t>
+          <t>globular</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Coil</t>
+          <t>Globular</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>protein_classification_type_choices</t>
+          <t>protein_structure_type_2_choices</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>enzyme</t>
+          <t>rods</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Enzyme</t>
+          <t>Rods</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>protein_classification_type_choices</t>
+          <t>protein_thermodynamics_2_choices</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>hormone</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hormone</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>protein_classification_type_choices</t>
+          <t>protein_thermodynamics_2_choices</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>receptor</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Receptor</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>protein_classification_type_choices</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>transport</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>protein_synthesis_process_choices</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>in_vivo</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>In Vivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>protein_synthesis_process_choices</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>in_vitro</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>In Vitro</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>protein_synthesis_process_choices</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>in_silico</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>In Silico</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>protein_3d_structure_choices</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>protein_3d_structure_choices</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
           <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>disulfide_bond_type_choices</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>cystein</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Cystein</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>disulfide_bond_type_choices</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>hydrogen_bond</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Hydrogen bond</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>disulfide_bond_type_choices</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>imino_bond</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Imino bond</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>disulfide_bond_type_choices</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>van_der_waals</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Van der Waals</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>protein_synthesis_method_choices</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>in_vivo</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>In Vivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>protein_synthesis_method_choices</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>in_vitro</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>In Vitro</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>protein_synthesis_method_choices</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>in_silico</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>In Silico</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>protein_structure_type_choices</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>alpha_helix</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Alpha Helix</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>protein_structure_type_choices</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>beta_sheet</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Beta Sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>protein_structure_type_choices</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>coil</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Coil</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>protein_structure_type_choices</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>globular</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Globular</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>protein_structure_type_choices</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>rods</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Rods</t>
         </is>
       </c>
     </row>
